--- a/JSON-converter.xlsx
+++ b/JSON-converter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrian/Documents/Personal/Pesnik.db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E1DD2F-2982-DE45-A6AA-4B08BDAA6758}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8FEBFF-2E8A-8E4F-A19E-002573559FD0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="51200" windowHeight="28340" activeTab="1" xr2:uid="{3B3296F3-CFAF-43B5-A5FB-1B474682DE3E}"/>
   </bookViews>
